--- a/r4-core-151-gda-triple/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T14:14:36+00:00</t>
+    <t>2026-10-19T12:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-151-gda-triple/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:51:52+00:00</t>
+    <t>2026-10-19T13:41:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4472,10 +4472,10 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>192</v>
@@ -5494,10 +5494,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -6184,10 +6184,10 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>192</v>
@@ -7206,10 +7206,10 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>21</v>
